--- a/2026/12/тьюринг.xlsx
+++ b/2026/12/тьюринг.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\W26\project\EGE-2026\2026\12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD4E347-227B-4027-9D8E-382FCB07530C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B74A165-0890-4A7D-AF87-C41FF39F8028}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="4" xr2:uid="{5C945562-84C8-4FA4-8D12-7626B398E1D5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{5C945562-84C8-4FA4-8D12-7626B398E1D5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="ДЕМО-26" sheetId="1" r:id="rId1"/>
     <sheet name="Лист1 (2)" sheetId="3" r:id="rId2"/>
     <sheet name="Лист1 (3)" sheetId="5" r:id="rId3"/>
     <sheet name="лашин" sheetId="6" r:id="rId4"/>
     <sheet name="лашин (2)" sheetId="7" r:id="rId5"/>
+    <sheet name="лашин (4)" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="4">
   <si>
     <t>λ</t>
   </si>
@@ -750,18 +751,62 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>242026</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82008CD8-2FD3-4948-9B93-42D1EB707317}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4638675" y="7467600"/>
+          <a:ext cx="9928951" cy="2028825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>400051</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133351</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -776,8 +821,171 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4057651" y="8877301"/>
-          <a:ext cx="7886699" cy="542924"/>
+          <a:off x="4400551" y="8048625"/>
+          <a:ext cx="10277474" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ru-RU" sz="1100">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>600730</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9115BAB-2530-4DCF-88AF-0F8B23862423}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2152649" y="981074"/>
+          <a:ext cx="10944881" cy="2238375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>42072</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F367406F-FDED-46CE-A778-D1B538D6634A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4743449" y="7172325"/>
+          <a:ext cx="9624223" cy="2533650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>180976</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Прямоугольник: скругленные углы 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{847D84F0-3724-4FA2-8B68-032863D7A1A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4448176" y="8858250"/>
+          <a:ext cx="10277474" cy="828675"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -1840,9 +2048,7 @@
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10"/>
-      <c r="O20" s="10">
-        <v>950</v>
-      </c>
+      <c r="O20" s="10"/>
     </row>
     <row r="21" spans="3:27" ht="26.25" x14ac:dyDescent="0.4">
       <c r="J21" s="10">
@@ -1854,9 +2060,7 @@
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10"/>
-      <c r="O21" s="10">
-        <v>19</v>
-      </c>
+      <c r="O21" s="10"/>
     </row>
     <row r="25" spans="3:27" ht="31.5" x14ac:dyDescent="0.5">
       <c r="C25" s="4"/>
@@ -1877,64 +2081,64 @@
         <v>0</v>
       </c>
       <c r="E26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7">
         <v>1</v>
       </c>
       <c r="G26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X26" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>0</v>
@@ -2012,64 +2216,64 @@
         <v>0</v>
       </c>
       <c r="E31" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="3">
         <v>0</v>
@@ -2079,6 +2283,250 @@
       </c>
       <c r="AA31" s="9" t="s">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80032881-105E-4D2F-9641-F6357A1AEF86}">
+  <dimension ref="C12:AA48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="7:16" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="20" spans="3:27" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="J20" s="10">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10">
+        <v>101</v>
+      </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="3:27" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="J21" s="10">
+        <v>20</v>
+      </c>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10">
+        <v>2</v>
+      </c>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+    </row>
+    <row r="25" spans="3:27" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="C25" s="4"/>
+      <c r="E25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="Y25" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" ht="26.25" x14ac:dyDescent="0.35">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7">
+        <v>0</v>
+      </c>
+      <c r="L26" s="7">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7">
+        <v>0</v>
+      </c>
+      <c r="O26" s="7">
+        <v>0</v>
+      </c>
+      <c r="P26" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0</v>
+      </c>
+      <c r="S26" s="7">
+        <v>0</v>
+      </c>
+      <c r="T26" s="7">
+        <v>0</v>
+      </c>
+      <c r="U26" s="7">
+        <v>0</v>
+      </c>
+      <c r="V26" s="7">
+        <v>0</v>
+      </c>
+      <c r="W26" s="7">
+        <v>0</v>
+      </c>
+      <c r="X26" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="C30" s="4"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" ht="26.25" x14ac:dyDescent="0.35">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="7">
+        <v>1</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1</v>
+      </c>
+      <c r="I31" s="7">
+        <v>1</v>
+      </c>
+      <c r="J31" s="7">
+        <v>1</v>
+      </c>
+      <c r="K31" s="7">
+        <v>1</v>
+      </c>
+      <c r="L31" s="7">
+        <v>1</v>
+      </c>
+      <c r="M31" s="7">
+        <v>1</v>
+      </c>
+      <c r="N31" s="7">
+        <v>1</v>
+      </c>
+      <c r="O31" s="7">
+        <v>1</v>
+      </c>
+      <c r="P31" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>1</v>
+      </c>
+      <c r="R31" s="7">
+        <v>1</v>
+      </c>
+      <c r="S31" s="7">
+        <v>1</v>
+      </c>
+      <c r="T31" s="7">
+        <v>0</v>
+      </c>
+      <c r="U31" s="7">
+        <v>1</v>
+      </c>
+      <c r="V31" s="7">
+        <v>0</v>
+      </c>
+      <c r="W31" s="7">
+        <v>1</v>
+      </c>
+      <c r="X31" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z48">
+        <v>601</v>
       </c>
     </row>
   </sheetData>
